--- a/Quellen/ki_prompts_robin.xlsx
+++ b/Quellen/ki_prompts_robin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Privat\HAW\Semester 3\IPJ 1\IPJ1-Pottkieker\Quellen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7DBA1F6-3F60-4294-BF55-5E657405C005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A757458B-643A-4434-9138-2724408F0472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,10 +25,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>df_ausbau = pd.concat([df_batterie, df_auto, df_schwungrad, df_wasserstoff, df_pump], axis=1)
 wie kann ich hier im resultierenden Dataframe die Spalten bezüglich des Datums nur einmal vorne haben und ansonsten nur die unterschiedlichen Speicherkapazitäten als weitere Spalten</t>
+  </si>
+  <si>
+    <t>speicher = []
+    for i in range(anzahl_tage_2030):
+        speicher.append(bestand2025 + wachstumsrate_2030 * (i+1))
+    speichername = f"Speicherkapazität {speicherart} [MWh]"
+    df_2030[speichername] = speicher
+dieser code war auf 15 Minuten Intervalle ausgelegt, wie kann ich ihn jetzt so auslegen, dass die tägliche Wachstumsrate verwendet wird, aber trotzdem jeder eintrag im Dataframe, also alle 15 Minuten einen Wert zugeordnet bekommt?</t>
   </si>
 </sst>
 </file>
@@ -64,10 +72,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -349,7 +360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="107.7109375" style="1" customWidth="1"/>
@@ -360,6 +371,11 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="1:1" ht="165" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Quellen/ki_prompts_robin.xlsx
+++ b/Quellen/ki_prompts_robin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Privat\HAW\Semester 3\IPJ 1\IPJ1-Pottkieker\Quellen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A757458B-643A-4434-9138-2724408F0472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5480F1E8-E791-4F10-9B09-DD2F0808C497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>df_ausbau = pd.concat([df_batterie, df_auto, df_schwungrad, df_wasserstoff, df_pump], axis=1)
 wie kann ich hier im resultierenden Dataframe die Spalten bezüglich des Datums nur einmal vorne haben und ansonsten nur die unterschiedlichen Speicherkapazitäten als weitere Spalten</t>
@@ -37,6 +37,9 @@
     speichername = f"Speicherkapazität {speicherart} [MWh]"
     df_2030[speichername] = speicher
 dieser code war auf 15 Minuten Intervalle ausgelegt, wie kann ich ihn jetzt so auslegen, dass die tägliche Wachstumsrate verwendet wird, aber trotzdem jeder eintrag im Dataframe, also alle 15 Minuten einen Wert zugeordnet bekommt?</t>
+  </si>
+  <si>
+    <t>ich kenne structures aus C, gibt es dafür ein äquivalent in python?</t>
   </si>
 </sst>
 </file>
@@ -360,7 +363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="107.7109375" style="1" customWidth="1"/>
@@ -376,6 +379,11 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Quellen/ki_prompts_robin.xlsx
+++ b/Quellen/ki_prompts_robin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Privat\HAW\Semester 3\IPJ 1\IPJ1-Pottkieker\Quellen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5480F1E8-E791-4F10-9B09-DD2F0808C497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D97321-2B4B-4509-895F-5C8A7B757DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>df_ausbau = pd.concat([df_batterie, df_auto, df_schwungrad, df_wasserstoff, df_pump], axis=1)
 wie kann ich hier im resultierenden Dataframe die Spalten bezüglich des Datums nur einmal vorne haben und ansonsten nur die unterschiedlichen Speicherkapazitäten als weitere Spalten</t>
@@ -40,6 +40,9 @@
   </si>
   <si>
     <t>ich kenne structures aus C, gibt es dafür ein äquivalent in python?</t>
+  </si>
+  <si>
+    <t>Wie kann ich dieses Dataframe jetzt am effizientesten sequentiell durchgehen?</t>
   </si>
 </sst>
 </file>
@@ -363,7 +366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="107.7109375" style="1" customWidth="1"/>
@@ -384,6 +387,11 @@
         <v>2</v>
       </c>
     </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Quellen/ki_prompts_robin.xlsx
+++ b/Quellen/ki_prompts_robin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Privat\HAW\Semester 3\IPJ 1\IPJ1-Pottkieker\Quellen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D97321-2B4B-4509-895F-5C8A7B757DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8EAE83B-860F-4B06-9369-3F51D6674C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>df_ausbau = pd.concat([df_batterie, df_auto, df_schwungrad, df_wasserstoff, df_pump], axis=1)
 wie kann ich hier im resultierenden Dataframe die Spalten bezüglich des Datums nur einmal vorne haben und ansonsten nur die unterschiedlichen Speicherkapazitäten als weitere Spalten</t>
@@ -43,6 +43,12 @@
   </si>
   <si>
     <t>Wie kann ich dieses Dataframe jetzt am effizientesten sequentiell durchgehen?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wie kann ich jetzt an genau den Tagen in der df_verlauf die den Tagen in der df_dunkelflaute entsprechen auf die Erzeugungswerte die Faktoren der Dunkelflaute anwenden? </t>
+  </si>
+  <si>
+    <t>wie kann ich diese sequentielle Schleife so anpassen, dass sie nur über einen bestimmten Bereich iteriert?</t>
   </si>
 </sst>
 </file>
@@ -366,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="107.7109375" style="1" customWidth="1"/>
@@ -392,6 +398,16 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Quellen/ki_prompts_robin.xlsx
+++ b/Quellen/ki_prompts_robin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Privat\HAW\Semester 3\IPJ 1\IPJ1-Pottkieker\Quellen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8EAE83B-860F-4B06-9369-3F51D6674C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F16EA7-0850-4587-9ED7-F35A1D550D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>df_ausbau = pd.concat([df_batterie, df_auto, df_schwungrad, df_wasserstoff, df_pump], axis=1)
 wie kann ich hier im resultierenden Dataframe die Spalten bezüglich des Datums nur einmal vorne haben und ansonsten nur die unterschiedlichen Speicherkapazitäten als weitere Spalten</t>
@@ -49,6 +49,12 @@
   </si>
   <si>
     <t>wie kann ich diese sequentielle Schleife so anpassen, dass sie nur über einen bestimmten Bereich iteriert?</t>
+  </si>
+  <si>
+    <t>Wie kann ich die Funktion "Verlauf_Speicher" effektiver machen, sowohl übersichtlicher als auch rechnerisch effizienter für den Computer? Gib mir nur Vorschläge und ändere nichts direkt im Code</t>
+  </si>
+  <si>
+    <t>Kannst du dann den aktuellen Stand auskommentieren und dann die neue Version einfügen? So kann ich die beiden Versionen vergleichen</t>
   </si>
 </sst>
 </file>
@@ -372,7 +378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="107.7109375" style="1" customWidth="1"/>
@@ -408,6 +414,16 @@
         <v>5</v>
       </c>
     </row>
+    <row r="7" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Quellen/ki_prompts_robin.xlsx
+++ b/Quellen/ki_prompts_robin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Privat\HAW\Semester 3\IPJ 1\IPJ1-Pottkieker\Quellen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F16EA7-0850-4587-9ED7-F35A1D550D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21619AFB-F3F9-4018-A80D-F44C31A279A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3870" yWindow="285" windowWidth="26205" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>df_ausbau = pd.concat([df_batterie, df_auto, df_schwungrad, df_wasserstoff, df_pump], axis=1)
 wie kann ich hier im resultierenden Dataframe die Spalten bezüglich des Datums nur einmal vorne haben und ansonsten nur die unterschiedlichen Speicherkapazitäten als weitere Spalten</t>
@@ -55,6 +55,12 @@
   </si>
   <si>
     <t>Kannst du dann den aktuellen Stand auskommentieren und dann die neue Version einfügen? So kann ich die beiden Versionen vergleichen</t>
+  </si>
+  <si>
+    <t>wie könnte ich diesen Abschnitt so gestalten, dass die Energie immer auf die verschiedenen Speicher aufgeteilt wird? Sage mir nur Lösungsvorschläge und ändere nichts am aktuellen Code</t>
+  </si>
+  <si>
+    <t>passe diese Funktion so an, dass nicht alle monate seperat betrachtet werden, sondern dass ein Balken für die Monate November bis einschließlich Februar und ein Balken für die restlichen Monate existiert</t>
   </si>
 </sst>
 </file>
@@ -378,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="107.7109375" style="1" customWidth="1"/>
@@ -424,6 +430,16 @@
         <v>7</v>
       </c>
     </row>
+    <row r="9" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Quellen/ki_prompts_robin.xlsx
+++ b/Quellen/ki_prompts_robin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Privat\HAW\Semester 3\IPJ 1\IPJ1-Pottkieker\Quellen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21619AFB-F3F9-4018-A80D-F44C31A279A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D423040C-068D-41D1-B602-DBF152B63A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3870" yWindow="285" windowWidth="26205" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10110" yWindow="3255" windowWidth="26205" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>df_ausbau = pd.concat([df_batterie, df_auto, df_schwungrad, df_wasserstoff, df_pump], axis=1)
 wie kann ich hier im resultierenden Dataframe die Spalten bezüglich des Datums nur einmal vorne haben und ansonsten nur die unterschiedlichen Speicherkapazitäten als weitere Spalten</t>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t>passe diese Funktion so an, dass nicht alle monate seperat betrachtet werden, sondern dass ein Balken für die Monate November bis einschließlich Februar und ein Balken für die restlichen Monate existiert</t>
+  </si>
+  <si>
+    <t>Kannst du mir für Option 2 eine Funktion schreiben die ich dann in jeder Loop aufrufen kann? Als Parameter die Gewichtungen und alle benötigten Daten, als Rückgabewerte die 3 Anteile der Speicher</t>
   </si>
 </sst>
 </file>
@@ -384,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="107.7109375" style="1" customWidth="1"/>
@@ -437,6 +440,11 @@
     </row>
     <row r="10" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Quellen/ki_prompts_robin.xlsx
+++ b/Quellen/ki_prompts_robin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Privat\HAW\Semester 3\IPJ 1\IPJ1-Pottkieker\Quellen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D423040C-068D-41D1-B602-DBF152B63A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA92D5A3-0BA4-41BA-AE14-7C41EB951CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10110" yWindow="3255" windowWidth="26205" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
